--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/04_feature_importance_top20/outputs/lasso_top20_feature_importance_with_categories.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/04_feature_importance_top20/outputs/lasso_top20_feature_importance_with_categories.xlsx
@@ -24,9 +24,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LASSO_Top20_Combined'!$A$1:$M$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LASSO_Top20_W2toW2'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'LASSO_Top20_W2toW3'!$A$1:$M$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CategorySummary'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CategorySummary'!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CategorySummaryWide'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SharedTop20'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SharedTop20'!$A$1:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InterpersonalSummary'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ridge_Top20_Reference'!$A$1:$M$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Logistic_Top20_Reference'!$A$1:$M$41</definedName>
@@ -562,7 +562,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.7755</v>
+        <v>-0.7733</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.7755</v>
+        <v>0.7733</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>14.10282056411283</v>
+        <v>14.24203915501777</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.6368</v>
+        <v>0.6362</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.6368</v>
+        <v>0.6362</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11.58049791776537</v>
+        <v>11.71703777372599</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.4016</v>
+        <v>-0.3979</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.4016</v>
+        <v>0.3979</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.3032788375857</v>
+        <v>7.328213345120357</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.3412</v>
+        <v>0.3405</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.3412</v>
+        <v>0.3405</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6.204877339104185</v>
+        <v>6.271064699707167</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2912</v>
+        <v>-0.2881</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.2912</v>
+        <v>0.2881</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.295604575460548</v>
+        <v>5.306002173232407</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -945,13 +945,13 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.2832</v>
+        <v>-0.281</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.2832</v>
+        <v>0.281</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.150120933277566</v>
+        <v>5.175239884339836</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -986,31 +986,31 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Help-Seeking</t>
+          <t>Online Perspective Seeking</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>v54_E</t>
+          <t>v26_B</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.255</v>
+        <v>0.2516</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.255</v>
+        <v>0.2516</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.637291094582554</v>
+        <v>4.63377350498186</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K8" s="3" t="b">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>v54_12;v54_16</t>
+          <t>v26_4;v26_5;v26_6</t>
         </is>
       </c>
     </row>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Online Perspective Seeking</t>
+          <t>Help-Seeking</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>v26_B</t>
+          <t>v54_E</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.2537</v>
+        <v>-0.2516</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.2537</v>
+        <v>0.2516</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.613650002727819</v>
+        <v>4.63377350498186</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K9" s="3" t="b">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>v26_4;v26_5;v26_6</t>
+          <t>v54_12;v54_16</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1634</v>
+        <v>0.1665</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.1634</v>
+        <v>0.1665</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.971503391587409</v>
+        <v>3.06646776064976</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1543</v>
+        <v>0.1558</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.1543</v>
+        <v>0.1558</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.806015748604267</v>
+        <v>2.869403466121517</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.1442</v>
+        <v>0.1416</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1442</v>
+        <v>0.1416</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.622342650348252</v>
+        <v>2.607878888336372</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.1362</v>
+        <v>-0.1392</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.1362</v>
+        <v>0.1392</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.476859008165269</v>
+        <v>2.563677551245925</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.1235</v>
+        <v>-0.1069</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.1235</v>
+        <v>0.1069</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.245903726199786</v>
+        <v>1.96880122290366</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1029</v>
+        <v>0.1063</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1029</v>
+        <v>0.1063</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.871283347578607</v>
+        <v>1.957750888631048</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.1006</v>
+        <v>0.1035</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.1006</v>
+        <v>0.1035</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.829456800450999</v>
+        <v>1.906182662025526</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1481,42 +1481,42 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Online Total Nominations, Observed Count</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>ip_online_total</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.0983</v>
+        <v>-0.0994</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.0983</v>
+        <v>0.0994</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.787630253323392</v>
+        <v>1.830672044496013</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K17" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
+          <t>Observed online friendship and online negative nominations, sent and received</t>
         </is>
       </c>
     </row>
@@ -1536,27 +1536,27 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Responsible Decision-Making</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v54_F</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-0.0954</v>
+        <v>-0.0989</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.0954</v>
+        <v>0.0989</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.734892433032061</v>
+        <v>1.82146343260217</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v54_17;v54_19;v54_20</t>
         </is>
       </c>
     </row>
@@ -1591,31 +1591,31 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Responsible Decision-Making</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>v54_F</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.0985</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0985</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.696702976959028</v>
+        <v>1.814096543087095</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v54_17;v54_19;v54_20</t>
+          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
         </is>
       </c>
     </row>
@@ -1646,31 +1646,31 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Victimization</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.0924</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0924</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.413009874702214</v>
+        <v>1.701751477982209</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K20" s="3" t="b">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -1701,27 +1701,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Social Feedback Dependency</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>v23_C</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.075</v>
+        <v>0.0801</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.075</v>
+        <v>0.0801</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.363909145465457</v>
+        <v>1.475219625393668</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>v23_7;v23_8;v23_9</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-0.3801</v>
+        <v>-0.38</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3801</v>
+        <v>0.38</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>12.77647058823529</v>
+        <v>12.8235413221746</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2715</v>
+        <v>0.2727</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.2715</v>
+        <v>0.2727</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>9.126050420168069</v>
+        <v>9.202578206728985</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.1507</v>
+        <v>-0.1492</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.1507</v>
+        <v>0.1492</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>5.065546218487395</v>
+        <v>5.03492727702224</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1417</v>
+        <v>0.1406</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.1417</v>
+        <v>0.1406</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.763025210084034</v>
+        <v>4.744710289204603</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.1297</v>
+        <v>-0.1289</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.1297</v>
+        <v>0.1289</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.359663865546218</v>
+        <v>4.349880201127122</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.1292</v>
+        <v>-0.1267</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.1292</v>
+        <v>0.1267</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.342857142857143</v>
+        <v>4.275638646104006</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1287</v>
+        <v>0.126</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.1287</v>
+        <v>0.126</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.326050420168068</v>
+        <v>4.252016333142105</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.1213</v>
+        <v>-0.122</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.1213</v>
+        <v>0.122</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.077310924369748</v>
+        <v>4.117031687645531</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2196,42 +2196,42 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Help-Seeking</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>ip_reciprocal_friend_count_rate_class</t>
+          <t>v54_E</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.1134</v>
+        <v>-0.1021</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.1134</v>
+        <v>0.1021</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.811764705882353</v>
+        <v>3.445483076300071</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K30" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Observed mutual friendship nominations / same-class respondents minus 1</t>
+          <t>v54_12;v54_16</t>
         </is>
       </c>
     </row>
@@ -2251,42 +2251,42 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Help-Seeking</t>
+          <t>Reciprocal Friendship Ties, Observed Count</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>v54_E</t>
+          <t>ip_reciprocal_friend_count</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.1037</v>
+        <v>0.101</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.1037</v>
+        <v>0.101</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3.485714285714286</v>
+        <v>3.408362298788513</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K31" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L31" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>v54_12;v54_16</t>
+          <t>Observed mutual friendship nominations</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         <v>0.1009</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.391596638655462</v>
+        <v>3.404987682651099</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.0919</v>
+        <v>0.091</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.0919</v>
+        <v>0.091</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.089075630252101</v>
+        <v>3.070900685047076</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2416,42 +2416,42 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Online Total Nominations, Respondent-Class-Normalized</t>
+          <t>Selective Positive Sharing</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>ip_online_total_rate_class</t>
+          <t>v23_A</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.971428571428572</v>
+        <v>2.841426787702899</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K34" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L34" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Observed online friendship and online negative nominations, sent and received / same-class respondents minus 1</t>
+          <t>v23_1;v23_2;v23_3</t>
         </is>
       </c>
     </row>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Selective Positive Sharing</t>
+          <t>Online-Offline Discrepancy &amp; Immersion</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>v23_A</t>
+          <t>v25_C</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.083</v>
+        <v>0.0805</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.083</v>
+        <v>0.0805</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.789915966386554</v>
+        <v>2.716565990618567</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>v23_1;v23_2;v23_3</t>
+          <t>v25_7;v25_8;v25_9;v25_10;v25_11;v25_12;v25_13;v25_14;v25_15</t>
         </is>
       </c>
     </row>
@@ -2526,42 +2526,42 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Online-Offline Discrepancy &amp; Immersion</t>
+          <t>Online Total Nominations, Observed Count</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>v25_C</t>
+          <t>ip_online_total</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0806</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0806</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.709243697478992</v>
+        <v>2.527587486923362</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K36" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L36" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>v25_7;v25_8;v25_9;v25_10;v25_11;v25_12;v25_13;v25_14;v25_15</t>
+          <t>Observed online friendship and online negative nominations, sent and received</t>
         </is>
       </c>
     </row>
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0722</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.403361344537815</v>
+        <v>2.436472851213174</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.0692</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.0692</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.326050420168067</v>
+        <v>2.298113589579185</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2705,13 +2705,13 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.068</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.068</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.285714285714286</v>
+        <v>2.264367428205042</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Fear of Missing Out &amp; Social Anxiety</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v27_A</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2760,17 +2760,17 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-0.0591</v>
+        <v>0.0601</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.0591</v>
+        <v>0.0601</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.986554621848739</v>
+        <v>2.028144298586036</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K40" s="3" t="b">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v27_1;v27_2;v27_3</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Fear of Missing Out &amp; Social Anxiety</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>v27_A</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2815,17 +2815,17 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.0578</v>
+        <v>-0.059</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.0578</v>
+        <v>0.059</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1.942857142857143</v>
+        <v>1.991023521074478</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K41" s="3" t="b">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>v27_1;v27_2;v27_3</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -3072,13 +3072,13 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.7557</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.772</v>
+        <v>0.7557</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>14.63895631067961</v>
+        <v>16.82136894824708</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -3127,13 +3127,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11.99370449029126</v>
+        <v>13.70061213133</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.3937</v>
+        <v>-0.3603</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.3937</v>
+        <v>0.3603</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.465488470873787</v>
+        <v>8.020033388981638</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6.392217839805825</v>
+        <v>7.091819699499166</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -3278,27 +3278,27 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v1_male</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2887</v>
+        <v>-0.2739</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.2887</v>
+        <v>0.2739</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.474438713592233</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -3333,27 +3333,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>v1_male</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.2819</v>
+        <v>-0.2733</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.2819</v>
+        <v>0.2733</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.083472454090151</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
         </is>
       </c>
     </row>
@@ -3402,13 +3402,13 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.750075849514563</v>
+        <v>5.150806900389538</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2497</v>
+        <v>-0.2233</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.2497</v>
+        <v>0.2233</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.734905946601941</v>
+        <v>4.970506399554814</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -3498,27 +3498,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Online Coping and Support Seeking under Distress</t>
+          <t>Cyberbullying Victimization (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>v22</t>
+          <t>v38</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1598</v>
+        <v>0.1499</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.1598</v>
+        <v>0.1499</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>3.030188106796116</v>
+        <v>3.33667223149694</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
+          <t>v38</t>
         </is>
       </c>
     </row>
@@ -3553,27 +3553,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Victimization (including Misinformation-related)</t>
+          <t>Online Coping and Support Seeking under Distress</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v22</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1475</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1475</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.910725121359223</v>
+        <v>3.283249860879244</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
         </is>
       </c>
     </row>
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.688865291262136</v>
+        <v>2.844741235392321</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.133</v>
+        <v>-0.1195</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.133</v>
+        <v>0.1195</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.521996359223301</v>
+        <v>2.659988870339455</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -3718,42 +3718,42 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sent Positive Tie Ratio</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ip_sent_like_ratio</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.1154</v>
+        <v>0.1001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.1154</v>
+        <v>0.1001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.188258495145631</v>
+        <v>2.228158041179744</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Observed friend nominations sent / all observed nominations sent</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -3773,42 +3773,42 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Outgoing Friendship Nominations, Respondent-Class-Normalized</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>ip_out_friend_total_rate_class</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1133</v>
+        <v>-0.0859</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1133</v>
+        <v>0.0859</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.1484375</v>
+        <v>1.912075681691709</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Observed online + offline friend nominations sent / same-class respondents minus 1</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -3828,27 +3828,27 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.894341626213592</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
         </is>
       </c>
     </row>
@@ -3883,27 +3883,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.742904841402337</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
@@ -3938,27 +3938,27 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Sent Positive Tie Ratio</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>ip_sent_like_ratio</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0731</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.788152305825243</v>
+        <v>1.627156371730662</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -3969,11 +3969,11 @@
         <v>1</v>
       </c>
       <c r="L18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>Observed friend nominations sent / all observed nominations sent</t>
         </is>
       </c>
     </row>
@@ -3993,42 +3993,42 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Social Awareness &amp; Relationship Skills</t>
+          <t>Incoming Friendship Nominations, Observed Count</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>v54_D</t>
+          <t>ip_in_friend_total</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.776774878640777</v>
+        <v>1.397885364496383</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v54_10;v54_11;v54_13;v54_14;v54_15</t>
+          <t>Observed online + offline friend nominations received</t>
         </is>
       </c>
     </row>
@@ -4048,31 +4048,31 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Responsible Decision-Making</t>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>v54_F</t>
+          <t>v40</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.0859</v>
+        <v>0.0562</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.0859</v>
+        <v>0.0562</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.628868325242719</v>
+        <v>1.250973845297718</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K20" s="3" t="b">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>v54_17;v54_19;v54_20</t>
+          <t>v40</t>
         </is>
       </c>
     </row>
@@ -4103,27 +4103,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Online Total Nominations, Respondent-Class-Normalized</t>
+          <t>Responsible Decision-Making</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ip_online_total_rate_class</t>
+          <t>v54_F</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0545</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0545</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.501820388349515</v>
+        <v>1.213132999443517</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -4134,11 +4134,11 @@
         <v>1</v>
       </c>
       <c r="L21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Observed online friendship and online negative nominations, sent and received / same-class respondents minus 1</t>
+          <t>v54_17;v54_19;v54_20</t>
         </is>
       </c>
     </row>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-0.3827</v>
+        <v>-0.3822</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3827</v>
+        <v>0.3822</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>17.38992138864906</v>
+        <v>17.20691518098326</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -4227,13 +4227,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.91470895624119</v>
+        <v>10.80947235728435</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -4282,13 +4282,13 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.1453</v>
+        <v>-0.1447</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.1453</v>
+        <v>0.1447</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -4337,13 +4337,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>5.920843368019265</v>
+        <v>5.821177741761211</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -4392,13 +4392,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>5.480074521743081</v>
+        <v>5.352962362686837</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.1167</v>
+        <v>-0.1157</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.1157</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.302858181487707</v>
+        <v>5.208896092202414</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-0.1018</v>
+        <v>-0.1003</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.1018</v>
+        <v>0.1003</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.625800881537693</v>
+        <v>4.515577165496129</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -4557,13 +4557,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.0987</v>
+        <v>-0.0969</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.0987</v>
+        <v>0.0969</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.484936611078292</v>
+        <v>4.36250675310643</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.257736174853456</v>
+        <v>4.218440482622007</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.289862316535647</v>
+        <v>3.331532504952278</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.0684</v>
+        <v>0.0679</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.0684</v>
+        <v>0.0679</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.108101967555777</v>
+        <v>3.056906176841347</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -4832,13 +4832,13 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.065</v>
+        <v>0.0654</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.065</v>
+        <v>0.0654</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.953605670922888</v>
+        <v>2.944354403025392</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-0.0569</v>
+        <v>-0.0589</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.0569</v>
+        <v>0.0589</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.585540964238651</v>
+        <v>2.651719791103909</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -4928,31 +4928,31 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-0.0513</v>
+        <v>0.0506</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0513</v>
+        <v>0.0506</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.331076475666833</v>
+        <v>2.278047902034936</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K36" s="3" t="b">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -4983,31 +4983,31 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Victimization (including Misinformation-related)</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.0499</v>
+        <v>-0.0501</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0501</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.267460353523878</v>
+        <v>2.255537547271746</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K37" s="3" t="b">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -5038,27 +5038,27 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Parenting Practices and Parent–Child Interaction Quality (Support/Conflict/Monitoring)</t>
+          <t>Cyberbullying Victimization (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v38</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0495</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0495</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.262916344799382</v>
+        <v>2.228525121555916</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
+          <t>v38</t>
         </is>
       </c>
     </row>
@@ -5093,27 +5093,27 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Parenting Practices and Parent–Child Interaction Quality (Support/Conflict/Monitoring)</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.231108283727905</v>
+        <v>2.183504412029534</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
         </is>
       </c>
     </row>
@@ -5148,27 +5148,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Fear of Missing Out &amp; Social Anxiety</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>ip_reciprocal_friend_count_rate_class</t>
+          <t>v27_A</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.0482</v>
+        <v>0.0456</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.0482</v>
+        <v>0.0456</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>2.052944354403026</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -5179,11 +5179,11 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Observed mutual friendship nominations / same-class respondents minus 1</t>
+          <t>v27_1;v27_2;v27_3</t>
         </is>
       </c>
     </row>
@@ -5217,13 +5217,13 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.0444</v>
+        <v>0.0452</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.0444</v>
+        <v>0.0452</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.017539873676557</v>
+        <v>2.034936070592473</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.7557</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.772</v>
+        <v>0.7557</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>14.63895631067961</v>
+        <v>16.82136894824708</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -5424,13 +5424,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11.99370449029126</v>
+        <v>13.70061213133</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -5479,13 +5479,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.3937</v>
+        <v>-0.3603</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.3937</v>
+        <v>0.3603</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.465488470873787</v>
+        <v>8.020033388981638</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6.392217839805825</v>
+        <v>7.091819699499166</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -5575,27 +5575,27 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v1_male</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2887</v>
+        <v>-0.2739</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.2887</v>
+        <v>0.2739</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.474438713592233</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -5630,27 +5630,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>v1_male</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.2819</v>
+        <v>-0.2733</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.2819</v>
+        <v>0.2733</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.083472454090151</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
         </is>
       </c>
     </row>
@@ -5699,13 +5699,13 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.750075849514563</v>
+        <v>5.150806900389538</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2497</v>
+        <v>-0.2233</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.2497</v>
+        <v>0.2233</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.734905946601941</v>
+        <v>4.970506399554814</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -5795,27 +5795,27 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Online Coping and Support Seeking under Distress</t>
+          <t>Cyberbullying Victimization (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>v22</t>
+          <t>v38</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1598</v>
+        <v>0.1499</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.1598</v>
+        <v>0.1499</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>3.030188106796116</v>
+        <v>3.33667223149694</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
+          <t>v38</t>
         </is>
       </c>
     </row>
@@ -5850,27 +5850,27 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Victimization (including Misinformation-related)</t>
+          <t>Online Coping and Support Seeking under Distress</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v22</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1475</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1475</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.910725121359223</v>
+        <v>3.283249860879244</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v22_1;v22_2;v22_3;v22_4;v22_5;v22_6</t>
         </is>
       </c>
     </row>
@@ -5919,13 +5919,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.688865291262136</v>
+        <v>2.844741235392321</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -5974,13 +5974,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.133</v>
+        <v>-0.1195</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.133</v>
+        <v>0.1195</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.521996359223301</v>
+        <v>2.659988870339455</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -6015,42 +6015,42 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sent Positive Tie Ratio</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ip_sent_like_ratio</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.1154</v>
+        <v>0.1001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.1154</v>
+        <v>0.1001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.188258495145631</v>
+        <v>2.228158041179744</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Observed friend nominations sent / all observed nominations sent</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -6070,42 +6070,42 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Outgoing Friendship Nominations, Respondent-Class-Normalized</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>ip_out_friend_total_rate_class</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1133</v>
+        <v>-0.0859</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1133</v>
+        <v>0.0859</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.1484375</v>
+        <v>1.912075681691709</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Observed online + offline friend nominations sent / same-class respondents minus 1</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -6125,27 +6125,27 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.0999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.894341626213592</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
         </is>
       </c>
     </row>
@@ -6180,27 +6180,27 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.0959</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.742904841402337</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
@@ -6235,27 +6235,27 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Sent Positive Tie Ratio</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>ip_sent_like_ratio</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0731</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.788152305825243</v>
+        <v>1.627156371730662</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -6266,11 +6266,11 @@
         <v>1</v>
       </c>
       <c r="L18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>Observed friend nominations sent / all observed nominations sent</t>
         </is>
       </c>
     </row>
@@ -6290,42 +6290,42 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Social Awareness &amp; Relationship Skills</t>
+          <t>Incoming Friendship Nominations, Observed Count</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>v54_D</t>
+          <t>ip_in_friend_total</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.776774878640777</v>
+        <v>1.397885364496383</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v54_10;v54_11;v54_13;v54_14;v54_15</t>
+          <t>Observed online + offline friend nominations received</t>
         </is>
       </c>
     </row>
@@ -6345,31 +6345,31 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Responsible Decision-Making</t>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>v54_F</t>
+          <t>v40</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.0859</v>
+        <v>0.0562</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.0859</v>
+        <v>0.0562</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.628868325242719</v>
+        <v>1.250973845297718</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K20" s="3" t="b">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>v54_17;v54_19;v54_20</t>
+          <t>v40</t>
         </is>
       </c>
     </row>
@@ -6400,27 +6400,27 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Online Total Nominations, Respondent-Class-Normalized</t>
+          <t>Responsible Decision-Making</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ip_online_total_rate_class</t>
+          <t>v54_F</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>SEL / Resilience</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0545</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0545</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.501820388349515</v>
+        <v>1.213132999443517</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -6431,11 +6431,11 @@
         <v>1</v>
       </c>
       <c r="L21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Observed online friendship and online negative nominations, sent and received / same-class respondents minus 1</t>
+          <t>v54_17;v54_19;v54_20</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.3827</v>
+        <v>-0.3822</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.3827</v>
+        <v>0.3822</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>17.38992138864906</v>
+        <v>17.20691518098326</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>10.91470895624119</v>
+        <v>10.80947235728435</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -6676,13 +6676,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.1453</v>
+        <v>-0.1447</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.1453</v>
+        <v>0.1447</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.920843368019265</v>
+        <v>5.821177741761211</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -6786,13 +6786,13 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.480074521743081</v>
+        <v>5.352962362686837</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.1167</v>
+        <v>-0.1157</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.1157</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.302858181487707</v>
+        <v>5.208896092202414</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -6896,13 +6896,13 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-0.1018</v>
+        <v>-0.1003</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.1018</v>
+        <v>0.1003</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.625800881537693</v>
+        <v>4.515577165496129</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -6951,13 +6951,13 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.0987</v>
+        <v>-0.0969</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.0987</v>
+        <v>0.0969</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.484936611078292</v>
+        <v>4.36250675310643</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4.257736174853456</v>
+        <v>4.218440482622007</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -7061,13 +7061,13 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0861</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -7116,13 +7116,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3.289862316535647</v>
+        <v>3.331532504952278</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.0684</v>
+        <v>0.0679</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.0684</v>
+        <v>0.0679</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.108101967555777</v>
+        <v>3.056906176841347</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -7226,13 +7226,13 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.065</v>
+        <v>0.0654</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.065</v>
+        <v>0.0654</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.953605670922888</v>
+        <v>2.944354403025392</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -7281,13 +7281,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-0.0569</v>
+        <v>-0.0589</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.0569</v>
+        <v>0.0589</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.585540964238651</v>
+        <v>2.651719791103909</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -7322,31 +7322,31 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.0513</v>
+        <v>0.0506</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.0513</v>
+        <v>0.0506</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.331076475666833</v>
+        <v>2.278047902034936</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K16" s="3" t="b">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -7377,31 +7377,31 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying Victimization (including Misinformation-related)</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.0499</v>
+        <v>-0.0501</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0501</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.267460353523878</v>
+        <v>2.255537547271746</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K17" s="3" t="b">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v38</t>
+          <t>v49</t>
         </is>
       </c>
     </row>
@@ -7432,27 +7432,27 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Parenting Practices and Parent–Child Interaction Quality (Support/Conflict/Monitoring)</t>
+          <t>Cyberbullying Victimization (including Misinformation-related)</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>v38</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0495</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0495</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.262916344799382</v>
+        <v>2.228525121555916</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
+          <t>v38</t>
         </is>
       </c>
     </row>
@@ -7487,27 +7487,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Parenting Practices and Parent–Child Interaction Quality (Support/Conflict/Monitoring)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0485</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2.231108283727905</v>
+        <v>2.183504412029534</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v6_1;v6_2;v6_3;v6_4;v6_5;v6_6;v6_7;v6_8;v6_9;v6_10</t>
         </is>
       </c>
     </row>
@@ -7542,27 +7542,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Fear of Missing Out &amp; Social Anxiety</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ip_reciprocal_friend_count_rate_class</t>
+          <t>v27_A</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0482</v>
+        <v>0.0456</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.0482</v>
+        <v>0.0456</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>2.052944354403026</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -7573,11 +7573,11 @@
         <v>1</v>
       </c>
       <c r="L20" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Observed mutual friendship nominations / same-class respondents minus 1</t>
+          <t>v27_1;v27_2;v27_3</t>
         </is>
       </c>
     </row>
@@ -7611,13 +7611,13 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.0444</v>
+        <v>0.0452</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.0444</v>
+        <v>0.0452</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.017539873676557</v>
+        <v>2.034936070592473</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7709,13 +7709,13 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>42.2386984223301</v>
+        <v>44.72565386755705</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>7.039783070388349</v>
+        <v>8.94513077351141</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -7741,10 +7741,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.163304004854369</v>
+        <v>8.928213689482472</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4.081652002427185</v>
+        <v>4.464106844741236</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -7770,10 +7770,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>18.48263046116505</v>
+        <v>20.09794101279911</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3.69652609223301</v>
+        <v>4.019588202559822</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -7796,13 +7796,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.805066747572814</v>
+        <v>8.558708959376739</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2.402533373786407</v>
+        <v>2.139677239844185</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -7825,13 +7825,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5.838516383495145</v>
+        <v>3.025041736227045</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.946172127831715</v>
+        <v>1.512520868113522</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -7857,10 +7857,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -7886,10 +7886,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -7915,10 +7915,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>37.04730313082199</v>
+        <v>36.59733477399605</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>9.261825782705499</v>
+        <v>9.149333693499011</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -7944,10 +7944,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10.15131549052574</v>
+        <v>10.04412029533586</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.383771830175247</v>
+        <v>3.348040098445286</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>24.7557595310583</v>
+        <v>26.38663785341257</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4.125959921843049</v>
+        <v>3.769519693344653</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -8002,10 +8002,10 @@
         <v>4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>9.469714181851227</v>
+        <v>9.485863497208717</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.367428545462807</v>
+        <v>2.371465874302179</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -8024,25 +8024,25 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.190212205207434</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -8053,58 +8053,29 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>W2 -&gt; W3</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Delinquency / Risk Behavior</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>3.907847503067205</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>3.907847503067205</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8159,16 +8130,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42.2386984223301</v>
+        <v>44.72565386755705</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37.04730313082199</v>
+        <v>36.59733477399605</v>
       </c>
     </row>
     <row r="3">
@@ -8181,13 +8152,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8.163304004854369</v>
+        <v>8.928213689482472</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10.15131549052574</v>
+        <v>10.04412029533586</v>
       </c>
     </row>
     <row r="4">
@@ -8200,13 +8171,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18.48263046116505</v>
+        <v>20.09794101279911</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>24.7557595310583</v>
+        <v>26.38663785341257</v>
       </c>
     </row>
     <row r="5">
@@ -8216,16 +8187,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.805066747572814</v>
+        <v>8.558708959376739</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9.469714181851227</v>
+        <v>9.485863497208717</v>
       </c>
     </row>
     <row r="6">
@@ -8235,17 +8206,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5.838516383495145</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2.190212205207434</v>
-      </c>
+        <v>3.025041736227045</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -8257,13 +8224,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>6.514496668467496</v>
       </c>
     </row>
     <row r="8">
@@ -8276,13 +8243,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1.818492111650485</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>3.876283090221502</v>
       </c>
     </row>
   </sheetData>
@@ -8297,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8384,19 +8351,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.772</v>
+        <v>-0.7557</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>14.63895631067961</v>
+        <v>16.82136894824708</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.3827</v>
+        <v>-0.3822</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>17.38992138864906</v>
+        <v>17.20691518098326</v>
       </c>
       <c r="J2" s="3" t="b">
         <v>1</v>
@@ -8422,19 +8389,19 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.6155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>11.99370449029126</v>
+        <v>13.70061213133</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.2402</v>
+        <v>0.2401</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>10.91470895624119</v>
+        <v>10.80947235728435</v>
       </c>
       <c r="J3" s="3" t="b">
         <v>1</v>
@@ -8460,10 +8427,10 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.3937</v>
+        <v>-0.3603</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7.465488470873787</v>
+        <v>8.020033388981638</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>9</v>
@@ -8472,7 +8439,7 @@
         <v>-0.09370000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4.257736174853456</v>
+        <v>4.218440482622007</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -8498,19 +8465,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.3371</v>
+        <v>0.3186</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6.392217839805825</v>
+        <v>7.091819699499166</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.1206</v>
+        <v>0.1189</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.480074521743081</v>
+        <v>5.352962362686837</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -8519,36 +8486,36 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v1_male</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.2887</v>
+        <v>-0.2739</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.474438713592233</v>
+        <v>6.096828046744574</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1167</v>
+        <v>-0.1447</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.302858181487707</v>
+        <v>6.514496668467496</v>
       </c>
       <c r="J6" s="3" t="b">
         <v>1</v>
@@ -8557,36 +8524,36 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>v1_male</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.2819</v>
+        <v>-0.2733</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.345494538834951</v>
+        <v>6.083472454090151</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1453</v>
+        <v>-0.1157</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>6.602444676693779</v>
+        <v>5.208896092202414</v>
       </c>
       <c r="J7" s="3" t="b">
         <v>1</v>
@@ -8612,19 +8579,19 @@
         <v>7</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.2505</v>
+        <v>0.2314</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4.750075849514563</v>
+        <v>5.150806900389538</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.1303</v>
+        <v>0.1293</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>5.920843368019265</v>
+        <v>5.821177741761211</v>
       </c>
       <c r="J8" s="3" t="b">
         <v>1</v>
@@ -8650,19 +8617,19 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.2497</v>
+        <v>-0.2233</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.734905946601941</v>
+        <v>4.970506399554814</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-0.0987</v>
+        <v>-0.0969</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.484936611078292</v>
+        <v>4.36250675310643</v>
       </c>
       <c r="J9" s="3" t="b">
         <v>1</v>
@@ -8685,22 +8652,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.1535</v>
+        <v>0.1499</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.910725121359223</v>
+        <v>3.33667223149694</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0495</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.267460353523878</v>
+        <v>2.228525121555916</v>
       </c>
       <c r="J10" s="3" t="b">
         <v>1</v>
@@ -8726,19 +8693,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.1418</v>
+        <v>0.1278</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.688865291262136</v>
+        <v>2.844741235392321</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.0498</v>
+        <v>0.0485</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.262916344799382</v>
+        <v>2.183504412029534</v>
       </c>
       <c r="J11" s="3" t="b">
         <v>1</v>
@@ -8761,22 +8728,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2.228158041179744</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>0.0999</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1.894341626213592</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="H12" s="3" t="n">
-        <v>0.0491</v>
+        <v>0.0506</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.231108283727905</v>
+        <v>2.278047902034936</v>
       </c>
       <c r="J12" s="3" t="b">
         <v>1</v>
@@ -8785,36 +8752,36 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>v49</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0859</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1.912075681691709</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>0.0959</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>1.818492111650485</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="H13" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.0501</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.907847503067205</v>
+        <v>2.255537547271746</v>
       </c>
       <c r="J13" s="3" t="b">
         <v>1</v>
@@ -8823,43 +8790,119 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>v49</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Perceived Effectiveness of School-based Digital/Technology Learning</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.788152305825243</v>
+        <v>1.903171953255426</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-0.0513</v>
+        <v>0.0861</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.331076475666833</v>
+        <v>3.876283090221502</v>
       </c>
       <c r="J14" s="3" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>v34</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Physical/Offline Bullying Victimization</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bullying / Victimization</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1.742904841402337</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2.944354403025392</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>v40</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cyberbullying Perpetration (including Misinformation-related)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Bullying / Victimization</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1.250973845297718</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>2.034936070592473</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8879,7 +8922,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
-    <col width="57" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="74" customWidth="1" min="9" max="9"/>
   </cols>
@@ -8941,16 +8984,16 @@
         <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>9.801653519417474</v>
+        <v>5.19309961046188</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -8958,11 +9001,11 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Incoming Negative Nominations, Respondent-Class-Normalized; Outgoing Negative Nominations, Respondent-Class-Normalized; Received Network Valence, Respondent-Class-Normalized; Sent Network Valence, Respondent-Class-Normalized</t>
+          <t>Incoming Negative Nominations, Observed Count; Outgoing Negative Nominations, Observed Count; Received Network Valence, Observed; Reciprocal Friendship Ties, Observed Count; Sent Network Valence, Observed</t>
         </is>
       </c>
     </row>
@@ -8982,22 +9025,22 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.171718089698732</v>
+        <v>3.952818296416352</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Reciprocal Friendship Ties, Observed Count</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Incoming Friendship Nominations, Respondent-Class-Normalized; Offline Total Nominations, Respondent-Class-Normalized; Outgoing Friendship Nominations, Respondent-Class-Normalized; Received Positive Tie Ratio; Received Network Valence, Respondent-Class-Normalized; Reciprocal Negative Ties, Respondent-Class-Normalized; Sent Positive Tie Ratio; Sent Network Valence, Respondent-Class-Normalized</t>
+          <t>Incoming Friendship Nominations, Observed Count; Offline Total Nominations, Observed Count; Outgoing Negative Nominations, Observed Count; Outgoing Friendship Nominations, Observed Count; Received Positive Tie Ratio; Received Network Valence, Observed; Reciprocal Negative Ties, Observed Count; Sent Positive Tie Ratio</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9063,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -9128,13 +9171,13 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>-0.736</v>
+        <v>-0.7138</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.736</v>
+        <v>0.7138</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>14.19534022527388</v>
+        <v>14.35841731539034</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -9183,13 +9226,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.5873</v>
+        <v>0.5639</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.5873</v>
+        <v>0.5639</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11.32734145965129</v>
+        <v>11.34310944823286</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -9238,13 +9281,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>-0.365</v>
+        <v>-0.3463</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.365</v>
+        <v>0.3463</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>7.039808671501313</v>
+        <v>6.965984752479232</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -9293,13 +9336,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.3247</v>
+        <v>0.3158</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.3247</v>
+        <v>0.3158</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6.262536645579386</v>
+        <v>6.3524631384145</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -9334,27 +9377,27 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Family Cohesion and Support (Family Functioning)</t>
+          <t>Gender: Male (vs Female)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v1_male</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Demographic / Social Status</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.2795</v>
+        <v>-0.2752</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.2795</v>
+        <v>0.2752</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>5.390757599135937</v>
+        <v>5.53577535051194</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -9369,7 +9412,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
@@ -9389,27 +9432,27 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Gender: Male (vs Female)</t>
+          <t>Family Cohesion and Support (Family Functioning)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>v1_male</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Demographic / Social Status</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>-0.2793</v>
+        <v>-0.2705</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.2793</v>
+        <v>0.2705</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.386900169726895</v>
+        <v>5.441232675557703</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -9424,7 +9467,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v5_1;v5_2;v5_3;v5_4;v5_5;v5_6</t>
         </is>
       </c>
     </row>
@@ -9458,13 +9501,13 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.2443</v>
+        <v>0.2372</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.2443</v>
+        <v>0.2372</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.711850023144577</v>
+        <v>4.771387765775552</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -9513,13 +9556,13 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.2439</v>
+        <v>-0.2355</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.2439</v>
+        <v>0.2355</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.704135164326494</v>
+        <v>4.737191479089977</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -9568,13 +9611,13 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.1557</v>
+        <v>0.1549</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.1557</v>
+        <v>0.1549</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>3.003008794939053</v>
+        <v>3.115885180938588</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -9623,13 +9666,13 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1475</v>
+        <v>0.1455</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.1475</v>
+        <v>0.1455</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.844854189168339</v>
+        <v>2.926799831030113</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -9678,13 +9721,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.1385</v>
+        <v>0.1328</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1385</v>
+        <v>0.1328</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.671269865761457</v>
+        <v>2.67133345402611</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -9733,13 +9776,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0.1324</v>
+        <v>-0.1322</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.1324</v>
+        <v>0.1322</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.553618268785681</v>
+        <v>2.659264176372378</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -9774,42 +9817,42 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sent Positive Tie Ratio</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ip_sent_like_ratio</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>-0.1121</v>
+        <v>0.0997</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.1121</v>
+        <v>0.0997</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.162089183767937</v>
+        <v>2.005511636795204</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Observed friend nominations sent / all observed nominations sent</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -9829,27 +9872,27 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Perpetration</t>
+          <t>Delinquent and Health-Risk Behaviors</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Delinquency / Risk Behavior</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.0982</v>
+        <v>0.0919</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.0982</v>
+        <v>0.0919</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.893997839839531</v>
+        <v>1.848611027296683</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -9864,7 +9907,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>v36</t>
+          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9923,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -9898,13 +9941,13 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.0949</v>
+        <v>-0.0919</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.0949</v>
+        <v>0.0919</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.830350254590341</v>
+        <v>1.848611027296683</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -9939,42 +9982,42 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Delinquent and Health-Risk Behaviors</t>
+          <t>Sent Positive Tie Ratio</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>v42</t>
+          <t>ip_sent_like_ratio</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Delinquency / Risk Behavior</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.0912</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0912</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.809134392840611</v>
+        <v>1.834530203367329</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K17" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>v42_01;v42_02;v42_03;v42_04;v42_05;v42_06;v42_07;v42_08;v42_09;v42_10;v42_11;v42_12;v42_13</t>
+          <t>Observed friend nominations sent / all observed nominations sent</t>
         </is>
       </c>
     </row>
@@ -10008,13 +10051,13 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.0912</v>
+        <v>0.0887</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.0912</v>
+        <v>0.0887</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.758987810523068</v>
+        <v>1.784241546476777</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -10049,42 +10092,42 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Victimization</t>
+          <t>Online Total Nominations, Observed Count</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>ip_online_total</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.0809</v>
+        <v>-0.0853</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.0809</v>
+        <v>0.0853</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.560330195957414</v>
+        <v>1.715848973105627</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>Observed online friendship and online negative nominations, sent and received</t>
         </is>
       </c>
     </row>
@@ -10104,27 +10147,27 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Social Feedback Dependency</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>v23_C</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Online / Digital Life</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.0751</v>
+        <v>0.0844</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.0751</v>
+        <v>0.0844</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.448464743095202</v>
+        <v>1.697745056625028</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -10139,7 +10182,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>v23_7;v23_8;v23_9</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
@@ -10159,31 +10202,31 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Responsible Decision-Making</t>
+          <t>Social Feedback Dependency</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>v54_F</t>
+          <t>v23_C</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Online / Digital Life</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.07480000000000001</v>
+        <v>0.0731</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0731</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.442678598981639</v>
+        <v>1.470440327479734</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K21" s="3" t="b">
@@ -10194,7 +10237,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>v54_17;v54_19;v54_20</t>
+          <t>v23_7;v23_8;v23_9</t>
         </is>
       </c>
     </row>
@@ -10228,13 +10271,13 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-0.3259</v>
+        <v>-0.3256</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3259</v>
+        <v>0.3256</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>13.06369503347096</v>
+        <v>13.04278160551194</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -10283,13 +10326,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.2134</v>
+        <v>0.2141</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.2134</v>
+        <v>0.2141</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.554134765703292</v>
+        <v>8.576349943919242</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -10338,13 +10381,13 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>-0.1461</v>
+        <v>-0.145</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.1461</v>
+        <v>0.145</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>5.856415601074278</v>
+        <v>5.808364044223681</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -10393,13 +10436,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.121</v>
+        <v>0.1203</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.121</v>
+        <v>0.1203</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.850282599110114</v>
+        <v>4.818939272552475</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -10448,13 +10491,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.1196</v>
+        <v>-0.1192</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.1196</v>
+        <v>0.1192</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.794163626889005</v>
+        <v>4.774875821182502</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -10503,13 +10546,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.1174</v>
+        <v>-0.1159</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.1174</v>
+        <v>0.1159</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.705976670541548</v>
+        <v>4.642685467072584</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -10558,13 +10601,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.1165</v>
+        <v>0.1148</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.1165</v>
+        <v>0.1148</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.669900188399407</v>
+        <v>4.598622015702611</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -10599,12 +10642,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Help-Seeking</t>
+          <t>Self-Management</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>v54_E</t>
+          <t>v54_B</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -10613,13 +10656,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.0979</v>
+        <v>-0.0973</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.0979</v>
+        <v>0.0973</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.924319557461819</v>
+        <v>3.897612562089408</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -10634,7 +10677,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>v54_12;v54_16</t>
+          <t>v54_4;v54_5;v54_6</t>
         </is>
       </c>
     </row>
@@ -10654,12 +10697,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Self-Management</t>
+          <t>Help-Seeking</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>v54_B</t>
+          <t>v54_E</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -10668,13 +10711,13 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0965</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.876217581272297</v>
+        <v>3.865566415638519</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -10689,7 +10732,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>v54_4;v54_5;v54_6</t>
+          <t>v54_12;v54_16</t>
         </is>
       </c>
     </row>
@@ -10723,13 +10766,13 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.0867</v>
+        <v>0.0871</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.0867</v>
+        <v>0.0871</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3.475367779692949</v>
+        <v>3.48902419484057</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -10778,13 +10821,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.0741</v>
+        <v>0.0752</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.0741</v>
+        <v>0.0752</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.970297029702971</v>
+        <v>3.012337766383592</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -10833,13 +10876,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.805948611055438</v>
+        <v>2.792020509533728</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -10874,42 +10917,42 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Reciprocal Friendship Ties, Respondent-Class-Normalized</t>
+          <t>Parental Involvement in Schooling and Academic Monitoring</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>ip_reciprocal_friend_count_rate_class</t>
+          <t>v19</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Interpersonal Network</t>
+          <t>Family / Parenting</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.0687</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0687</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.729787148755361</v>
+        <v>2.751962826470117</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K34" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L34" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Observed mutual friendship nominations / same-class respondents minus 1</t>
+          <t>v19_1;v19_2;v19_3;v19_4;v19_5;v19_6;v19_7;v19_8;v19_9;v19_10</t>
         </is>
       </c>
     </row>
@@ -10929,31 +10972,31 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Parental Involvement in Schooling and Academic Monitoring</t>
+          <t>Physical/Offline Bullying Victimization</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>v19</t>
+          <t>v34</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Family / Parenting</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-0.0678</v>
+        <v>0.0664</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.0678</v>
+        <v>0.0664</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.717761654707981</v>
+        <v>2.65983015542381</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K35" s="3" t="b">
@@ -10964,7 +11007,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>v19_1;v19_2;v19_3;v19_4;v19_5;v19_6;v19_7;v19_8;v19_9;v19_10</t>
+          <t>v34</t>
         </is>
       </c>
     </row>
@@ -10984,27 +11027,27 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Physical/Offline Bullying Victimization</t>
+          <t>Reciprocal Friendship Ties, Observed Count</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>ip_reciprocal_friend_count</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Bullying / Victimization</t>
+          <t>Interpersonal Network</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.669659678518459</v>
+        <v>2.519628264701169</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -11015,11 +11058,11 @@
         <v>1</v>
       </c>
       <c r="L36" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>v34</t>
+          <t>Observed mutual friendship nominations</t>
         </is>
       </c>
     </row>
@@ -11053,13 +11096,13 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.0593</v>
+        <v>0.0613</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.0593</v>
+        <v>0.0613</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.377039323365535</v>
+        <v>2.455535971799391</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -11108,13 +11151,13 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-0.0592</v>
+        <v>-0.0588</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.0592</v>
+        <v>0.0588</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.373030825349741</v>
+        <v>2.355391764140362</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -11145,7 +11188,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -11163,13 +11206,13 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.0592</v>
+        <v>0.0584</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.0592</v>
+        <v>0.0584</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.373030825349741</v>
+        <v>2.339368690914917</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -11204,27 +11247,27 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Motivation &amp; Goal Setting</t>
+          <t>Physical/Offline Bullying Perpetration</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>v54_C</t>
+          <t>v36</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>SEL / Resilience</t>
+          <t>Bullying / Victimization</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.0523</v>
+        <v>0.0527</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.0523</v>
+        <v>0.0527</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.096444462259991</v>
+        <v>2.111039897452331</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -11239,7 +11282,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>v54_7;v54_8;v54_9</t>
+          <t>v36</t>
         </is>
       </c>
     </row>
@@ -11273,13 +11316,13 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.0518</v>
+        <v>0.0519</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.0518</v>
+        <v>0.0519</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.076401972181024</v>
+        <v>2.078993751001442</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
